--- a/Result/checksun_type/觸控面板.xlsx
+++ b/Result/checksun_type/觸控面板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>10.42</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>11.14</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>7084001.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6674277.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6674277</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>7830514.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>16190279.42</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>16190279.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-790786.255338965</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>7084001</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>7084001.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>10.4</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>12.26</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5716511.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>7729029.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>7729029.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>7861939.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>16694475.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>16694475.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-848245.8333365694</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5716511</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5716511.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>11.31</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6019396.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>8888224.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>8888224.800000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>7927764.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>16881886.4</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>16881886.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-753519.6649997002</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6019396</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6019396.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>10.68</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>12.37</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.37</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>8379435.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>9821389.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>9821389.800000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8116597.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>17170511.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>17170511.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-623737.1150541827</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>8379435</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8379435.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>10.9</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>12.43</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12.43</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>6172042.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>9102162.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>9102162</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>8119149.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>17256895.92</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>17256895.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-668918.4681657925</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>6172042</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6172042.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>11.09</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>12.49</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.49</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>12357764.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8986752.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>8986752.800000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>8218243.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>17307336.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>17307336.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-473066.9201764595</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>12357764</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>12357764.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>11.3</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>11.68</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12.55</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>11512487.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7994849.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7994849.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>8316682.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>17415976.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>17415976.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-839139.6758996788</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>11512487</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>11512487.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>11.4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>11.75</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12.6</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>10685221.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>6967303.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>6967303.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>8240687.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>17371210.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>17371210.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1241566.088507863</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>10685221</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>10685221.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>11.43</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>11.81</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>12.64</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4783296.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>6411806.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>6411806</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>8172263.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>17382904.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>17382904.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-1683483.674787129</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4783296</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4783296.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>11.87</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>12.68</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>12.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5594996.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>7136137.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>7136137</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>9165582.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>17622707.52</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>17622707.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1622320.9882294</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5594996</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5594996.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>11.39</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>11.91</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>12.72</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>7398247.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>7449735.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>7449735</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>9712675.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>17784815.8</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>17784815.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1563973.543567307</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>7398247</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7398247.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>52.54</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>53.95</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>53.42</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>53.42</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>54.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>698.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>698.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>581.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1407.16</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1407.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-132.0683859188558</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>54</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>52.36</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>53.36</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>53.36</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1308.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>876.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>876.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>648.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1422.36</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1422.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-77.92344321439953</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1308</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1308.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>52.42</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>54.28</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>53.32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1029.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>731.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>731.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>642.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1417.58</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1417.58</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-132.1476878075193</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1029</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1029.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>52.62</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>54.52</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>53.29</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>53.29</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>840.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>539.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>539.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>757.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1429.1</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1429.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-174.9984769474219</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>840</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>52.66</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>54.71</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>53.24</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>53.24</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>263.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>396.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>396.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>829.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1434.4</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1434.4</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-209.7139443991603</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>263</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>263.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>52.74000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>54.91</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>53.19</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>53.19</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>944.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>464.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>464.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1150.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1432.54</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1432.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-189.9962570302453</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>944</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>944.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>52.92</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>55.11</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>53.14</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>53.14</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>583.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>419.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>419.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1208.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1439.02</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1439.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-228.0068373235722</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>583</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>583.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>52.86</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>55.29</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>53.1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>552.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>552.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1235.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1443.06</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1443.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-235.4859935524833</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>66</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>52.86</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>55.46</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>53.05</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>53.05</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>126.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>974.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>974.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1485.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1469.6</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1469.6</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-182.3674312526243</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>126</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>53.22000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>55.61</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>53</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>605.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1262.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1262.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1501.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1495.2</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1495.2</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-106.3992197080893</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>605</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>54.06</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>52.95</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>52.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>718.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1836.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1836.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1499.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1510.5</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1510.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-45.3946596548933</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>718</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>718.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>17.65</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>18.08</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>19.07</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>15786.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>3498.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>3498</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1925.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>986.14</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>986.14</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1160.889933353634</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>15786</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>15786.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>17.56</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>19.1</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>374.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>387.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>387.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>380.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>687.62</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>687.62</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>5.400394870123876</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>374</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>374.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>17.56</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>19.15</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>106.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>429.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>429.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>384.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>690.18</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>690.1799999999999</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>5.793897219747805</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>106</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>17.64</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>18.27</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>19.2</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>776.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>445.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>445.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>390.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>697.38</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>697.38</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>34.8634042470768</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>776</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>776.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>17.74</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>19.26</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>448.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>352.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>352.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>331.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>691.26</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>691.26</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>3.360435563008366</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>448</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>17.92</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>19.31</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>233.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>353.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>353.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>326.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>685.96</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>685.96</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-6.620963827196874</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>233</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>233.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>18.14</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>19.37</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>19.37</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>584.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>372.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>372.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>325.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>685.74</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>685.74</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>2.39207146633828</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>584</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>584.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>18.18</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>19.42</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>185.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>339.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>339.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>295.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>689.84</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>689.84</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-22.42473780955208</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>185</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>18.22</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>18.62</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>19.48</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>19.48</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>311.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>336.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>336</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>288.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>686.22</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>686.22</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-14.32643899619717</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>311</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>311.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>18.23</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>18.68</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>19.53</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>19.53</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>455.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>310.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>310.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>272.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>688.48</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>688.48</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-15.74578215582596</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>455</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>455.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>18.23</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>18.76</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>328.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>300</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>238.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>691.92</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>691.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-32.63963730687328</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>328</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>328.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>40.79</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>42.49</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>44.58</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>44.58</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>4102.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2757.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2757.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>3670.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2178.26</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2178.26</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>58.73819963476308</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>4102</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4102.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>40.86</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>42.65</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>44.71</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>44.71</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>3586.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2755.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2755.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3432.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2129.54</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2129.54</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-5.025251621802454</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>3586</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>3586.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>40.92</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>42.82</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>44.84</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1988.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>3256.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>3256.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3575.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2072.16</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2072.16</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-40.65070871611761</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1988</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1988.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>40.96</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>44.99</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>44.99</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>3041.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>3567.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>3567.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3604.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2036.44</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2036.44</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>81.12187788900792</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3041</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3041.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>41.16</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>43.16</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>45.13</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>45.13</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1071.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>4580.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>4580.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3634.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1994.96</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1994.96</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>139.3640774002943</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1071</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1071.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>41.65000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>43.33</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>45.28</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>45.28</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>4093.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>4583.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>4583.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>4024.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1978.44</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1978.44</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>428.6613596521215</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>4093</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>4093.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>42.12</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>45.42</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>45.42</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6088.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4110.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4110</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>4006.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1897.56</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1897.56</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>502.8481428814416</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6088</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6088.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>42.67</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>43.72</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>45.57</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>3545.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>3894.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>3894.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3919.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1788.38</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1788.38</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>377.1203995347046</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>3545</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>3545.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>43.96</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>45.72</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>45.72</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>8106.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3640.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3640.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3860.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1742.88</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1742.88</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>456.5050376274121</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>8106</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>8106.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>43.59</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>44.14</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>45.85</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1085.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2688.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2688.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>3475.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1592.36</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1592.36</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>64.92934070172942</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1085</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1085.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>43.63</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>45.96</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1726.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3465.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3465.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3502.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1578.56</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1578.56</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>255.4665829256933</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1726</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1726.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>20.36</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>21.79</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>21.79</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>7394.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>5300.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>5300.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>6869.0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>7822.94</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>7822.94</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-28.28632061396729</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>7394</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>7394.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>20.02</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>21.83</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>21.83</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>3419.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>5214.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>5214.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>6394.6</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>8401.28</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>8401.280000000001</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-181.1253228560054</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3419</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3419.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>19.82</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>21.91</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>3853.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>7138.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>7138</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>6592.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>9146.44</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>9146.440000000001</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>32.89486404308445</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>3853</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>3853.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>19.8</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>20.44</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>6023.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>8657.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>8657.799999999999</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>6673.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>9575.96</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>9575.959999999999</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>290.9631716116728</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>6023</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>6023.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>19.88</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>22.12</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>22.12</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>5814.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>8699.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>8699.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>6353.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>9861.4</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>9861.4</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>416.7406405806687</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>5814</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>5814.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>19.98</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>22.22</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>22.22</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>6965.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>8437.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>8437.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>6234.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>10207.54</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>10207.54</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>603.9320019442102</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>6965</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>6965.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>20.24</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>22.34</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>13035.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>7574.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>7574.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>5905.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>10674.28</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>10674.28</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>726.4578038226919</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>13035</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>13035.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>20.41</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>20.91</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>22.46</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>11452.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>6047.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>6047.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>5008.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>11142.64</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>11142.64</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>225.1925992268552</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>11452</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>11452.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>20.44</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>6232.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>4689.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>4689.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>4452.7</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>12309.22</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>12309.22</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-329.3360001681567</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>6232</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>6232.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>20.41</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>22.68</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>4503.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>4007.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>4007.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4099.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>14826.9</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>14826.9</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-550.4719992978817</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>4503</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>4503.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>20.49</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>22.81</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>22.81</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>2650.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>4030.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>4030.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>4115.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>17118.32</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>17118.32</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-661.4708552225648</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>2650</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>2650.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>19.45</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>21.48</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>537.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>537.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1332.24</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1332.24</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-141.0385748025855</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>446</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>21.54</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>494.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>494.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>754.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1394.4</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1394.4</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-143.6359791514134</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>166</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>21.61</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>290.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>804.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>804</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>822.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1439.06</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1439.06</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-112.2167003943315</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>290</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>19.42</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>21.68</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1287.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>930.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>930.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>895.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1833.62</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1833.62</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-76.60999144155971</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1287</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1287.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>19.67</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>21.75</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>497.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>738.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>738.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>769.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1851.22</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1851.22</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-129.8286218146873</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>497</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>497.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>21.81</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>21.81</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>911.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>911.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>794.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1867.82</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1867.82</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-116.5756429972018</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>231</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1715.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1014.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1014.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>834.8</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1896.36</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1896.36</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-64.97940029375127</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1715</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1715.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>20.44</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>21.92</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>922.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>840.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>840.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>714.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1889.2</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1889.2</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-147.9497892783307</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>922</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>922.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>20.46</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>21.96</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>326.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>861.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>861.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>702.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2075.44</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2075.44</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-176.2307096392179</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>326</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>326.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>20.53</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1362.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>800.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>800.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>791.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2169.22</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2169.22</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-146.4809276676563</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1362</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1362.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>20.6</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>22.08</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>22.08</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>747.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>677.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>677.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>999.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2614.76</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2614.76</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-209.7497774344375</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>747</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>747.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>67.44000000000001</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>57.54</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>68305837.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>68193204.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>68193204</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>136229985.7</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>46606279.72</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>46606279.72</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-1579885.667524114</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>68305837</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>68305837.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>67.64000000000001</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>57.23</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>59064123.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>84222262.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>84222262.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>140379245.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>45652449.62</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>45652449.62</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>1268393.578065202</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>59064123</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>59064123.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>56.91</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>55041164.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>115240085.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>115240085.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>153170422.4</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>44737206.8</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>44737206.8</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>6282247.801119044</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>55041164</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>55041164.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>68.92</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>56.6</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>77457284.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>149719715.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>149719715</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>157079528.3</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>44057108.44</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>44057108.44</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>13651562.01972742</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>77457284</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>69.28</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>60.56</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>56.31</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>56.31</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>81097612.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>180244870.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>161062192.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>42670813.98</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>21289870.83132054</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>81097612</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>81097612.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>69.06</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>59.93</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>55.99</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>148451128.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>204266767.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>204266767.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>153514394.7</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>41211816.88</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>41211816.88</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>31051352.88962071</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>148451128</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>148451128.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>68.47999999999999</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>55.7</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>214153238.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>196536229.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>196536229.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>140950400.0</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>38471387.22</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>38471387.22</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>36670902.22684878</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>214153238</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>214153238.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>67.32000000000001</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>58.69</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>227439313.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>191100759.6</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>191100759.6</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>120375958.7</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>34338500.78</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>34338500.78</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>36349642.98621568</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>227439313</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>227439313.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>64.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>57.81</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>54.98</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>54.98</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>230083062.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>164439341.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>164439341.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>98801936.3</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>30095348.66</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>30095348.66</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>33168991.64294642</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>230083062</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>230083062.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>62.72000000000001</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>57.11</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>54.65</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>201207096.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>141879514.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>141879514.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>76590805.2</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>26134633.24</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>26134633.24</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>27157338.34388511</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>201207096</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>201207096.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>60.27999999999999</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>56.46</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>54.4</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>109798437.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>102762022.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>102762022</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>57072853.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>22355997.5</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>22355997.5</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>20693210.76151591</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>109798437</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>109798437.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>37.21</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>38.41</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>915.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1126.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1126.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1732.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2097.92</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2097.92</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-245.4020233382141</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>915</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>915.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>37.13</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>38.41</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>652.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1621.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1621.8</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1774.8</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2121.5</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2121.5</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-219.5949860126452</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>652</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>652.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>37.23</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>38.36</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>38.42</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>38.42</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>952.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1866.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1866.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1882.0</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2150.8</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2150.8</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-146.7065403328095</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>952</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>952.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>37.45</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>38.44</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>38.44</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>2025.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>2027.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>2027</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>2017.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2158.84</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2158.84</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-69.48352720687262</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>2025</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>2025.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>37.83</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>38.56</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>38.47</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>38.47</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1087.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1920.4</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1920.4</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>2024.4</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2161.76</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2161.76</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-71.64766819814531</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1087</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1087.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>38.19</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>38.62</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>38.5</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>3393.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>2339.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>2339</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>2767.3</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2159.12</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2159.12</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>28.31954710711307</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>3393</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>3393.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>38.68</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>38.68</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>38.52</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>1875.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1927.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1927.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>2511.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2157.84</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2157.84</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-76.95298628205774</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1875</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1875.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>38.98999999999999</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>38.71</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>38.55</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1755.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1897.6</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1897.6</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>2473.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2149.54</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2149.54</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-61.951141613657</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1755</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1755.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>39.14</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>38.54</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>1492.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>2008.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>2008</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>2476.8</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2182.48</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2182.48</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-25.4502513154539</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1492</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1492.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>39.33</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>38.66</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>38.54</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>3180.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>2128.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>2128.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>2407.1</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2303.76</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2303.76</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>55.78138665753113</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>3180</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>3180.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>38.61</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>38.56</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>38.56</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>1337.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>3195.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>3195.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>2342.5</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2591.58</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2591.58</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-11.02275147597402</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1337</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1337.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>12.44</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>13.8</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>726101414.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>522491393.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>522491393.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>500252244.3</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>951906310.08</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>951906310.08</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-27507192.40119457</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>726101414</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>726101414.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>12.32</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>13.81</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>13.81</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>298259044.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>458588598.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>458588598.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>469412312.7</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>952356783.44</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>952356783.4400001</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-51416436.28370804</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>298259044</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>298259044.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>12.31</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>13.83</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>13.83</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>653442603.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>539127122.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>539127122.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>523171176.0</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>958838697.5</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>958838697.5</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-37895943.748595</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>653442603</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>653442603.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>12.44</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>13.86</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>528064397.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>496768343.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>496768343.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>529229061.7</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>954039194.6</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>954039194.6</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-55282909.17169785</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>528064397</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>528064397.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>12.61</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>13.9</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>406589511.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>475101346.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>475101346.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>526608726.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>957961469.06</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>957961469.0599999</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-64713662.3771413</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>406589511</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>406589511.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>12.78</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>13.92</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>406587436.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>478013094.8</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>478013094.8</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>540193718.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>959510743.76</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>959510743.76</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-62859798.37144822</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>406587436</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>406587436.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>12.96</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>13.49</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>13.94</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>700951664.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>480236027.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>480236027.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>574567755.4</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>962186777.6</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>962186777.6</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-57966206.10004926</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>700951664</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>700951664.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>13.07</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>13.59</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>13.96</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>13.96</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>441648708.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>507215229.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>507215229.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>561036827.5</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>968670779.14</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>968670779.14</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-80444162.78019172</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>441648708</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>441648708.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>13.15</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>13.66</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>419729414.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>561689780.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>561689780.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>586608470.2</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>987821058.9</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>987821058.9</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-81900064.08110285</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>419729414</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>419729414.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>13.33</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>13.74</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>14</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>421148252.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>578116107.0</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>578116107</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>611710207.8</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>997706755.02</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>997706755.02</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-78706425.00807929</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>421148252</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>421148252.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>13.81</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>14.01</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>417702098.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>602374341.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>602374341.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>623134652.8</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>1016363202.4</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>1016363202.4</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-71485158.08204281</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>417702098</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>417702098.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>152.57</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>166.86</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>152.57</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>166.86</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>125439899.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>48021902.8</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>48021902.8</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>47800168.1</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>89823455.14</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>89823455.14</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>1180769.917360015</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>125439899</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>125439899.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>142.9</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>167.75</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>167.75</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>31020484.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>30084718.8</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>30084718.8</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>39591213.5</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>104685957.22</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>104685957.22</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-6228711.733160153</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>31020484</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>31020484.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>142.1</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>154.1</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>168.8</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>154.1</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>168.8</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>22124495.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>37616973.0</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>37616973</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>40918294.7</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>111448346.96</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>111448346.96</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-6474865.636290379</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>22124495</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>22124495.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>142.8</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>155.28</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>170.01</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>155.28</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>170.01</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>33277405.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>42064693.8</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>42064693.8</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>42527255.9</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>132973635.9</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>132973635.9</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-5642127.189466052</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>33277405</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>33277405.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>144.1</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>156.5</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>171.06</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>171.06</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>28247231.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>45996995.4</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>45996995.4</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>43521794.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>136817713.6</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>136817713.6</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-5445950.937236078</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>28247231</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>28247231.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>145.6</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>157.72</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>157.72</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>172</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>35753979.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>47578433.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>47578433.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>46597569.1</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>141288080.0</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>141288080</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-4432253.686291978</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>35753979</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>35753979.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>147.5</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>159.07</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>172.99</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>159.07</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>172.99</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>68681755.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>49097708.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>49097708.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>55804228.6</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>167430982.8</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>167430982.8</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-3630114.410432838</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>68681755</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>68681755.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>149.7</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>160.22</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>174.09</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>160.22</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>174.09</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>44363099.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>44219616.4</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>44219616.4</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>53918726.7</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>182491557.4</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>182491557.4</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-5882530.215975739</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>44363099</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>44363099.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>151.6</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>161.18</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>174.76</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>161.18</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>174.76</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>52938913.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>42989818.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>42989818</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>53643652.4</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>189421190.9</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>189421190.9</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-6284606.430466473</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>52938913</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>52938913.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>153.8</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>162.22</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>175.55</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>162.22</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>175.55</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>36154421.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>41046594.4</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>41046594.4</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>51813568.8</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>195834402.02</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>195834402.02</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-7553388.007222272</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>36154421</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>36154421.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>155.5</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>162.93</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>176.37</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>176.37</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>43350353.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>45616704.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>45616704.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>54463120.3</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>209025189.96</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>209025189.96</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-7297830.830901198</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>43350353</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>43350353.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>6.681999999999999</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>6.62</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>6.62</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>8560132.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>7431179.0</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>7431179</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>13619316.5</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>11572138.7</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>11572138.7</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-973726.8753598984</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>8560132</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>8560132.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>6.688</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>6.63</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>6.61</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>6.61</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>9583962.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>7534759.6</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>7534759.6</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>15493234.2</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>11588340.7</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>11588340.7</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-900199.7303417102</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>9583962</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>9583962.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>6.728</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>6.63</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>6.6</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>6012578.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>7923715.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>7923715</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>18245406.2</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>11538446.66</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>11538446.66</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-872707.0328035224</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>6012578</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>6012578.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>6.837999999999999</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>6.6</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>7579940.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>9606726.8</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>9606726.800000001</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>18073657.4</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>11538488.32</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>11538488.32</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-419615.356577415</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>7579940</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>7579940.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>6.948</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>6.59</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>5419283.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>13248740.2</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>13248740.2</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>17597751.6</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>11501211.36</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>11501211.36</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>74713.0864805039</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>5419283</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>5419283.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>7.025999999999999</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>6.59</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>9078035.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>19807454.0</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>19807454</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>17561051.1</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>11506339.1</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>11506339.1</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>1009727.216331799</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>9078035</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>9078035.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>7.056</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>6.58</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>6.58</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>11528739.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>23451708.8</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>23451708.8</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>17209108.4</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>11421206.58</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>11421206.58</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>1917390.858393226</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>11528739</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>11528739.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>7.062</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>6.63</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>6.57</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>14427637.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>28567097.4</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>28567097.4</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>16689696.4</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>11258374.24</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>11258374.24</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>2882999.530681223</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>14427637</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>14427637.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>6.901999999999999</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>6.55</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>25790007.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>26540588.0</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>26540588</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>16183234.9</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>11077478.22</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>11077478.22</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>3848880.00785403</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>25790007</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>25790007.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>6.74</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>6.58</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>6.54</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>6.54</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>38212852.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>21946763.0</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>21946763</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>14320002.5</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>10698794.14</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>10698794.14</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>3873852.474963253</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>38212852</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>38212852.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>6.553999999999999</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>6.53</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>27299309.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>15314648.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>15314648.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>11247961.7</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>10052298.34</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>10052298.34</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>2440156.44672774</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>27299309</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>27299309.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>20.27</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>20.99</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>20.99</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>3555489.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>3111394.2</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>3111394.2</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>3801751.0</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>4930246.16</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>4930246.16</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-341806.4899302381</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>3555489</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>3555489.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>20.18</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>20.57</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>20.99</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>20.99</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>2537809.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>2956870.6</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>2956870.6</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>4157510.4</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>5068545.2</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>5068545.2</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-389132.4258959754</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>2537809</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>2537809.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>20.18</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>20.61</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>21.02</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>3055963.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>3072935.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>3072935.4</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>4405890.0</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>5101526.1</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>5101526.1</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-333806.1763507435</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>3055963</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>3055963.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>20.26</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>21.06</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>2763187.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>3789911.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>3789911.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>4399515.9</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>5242936.7</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>5242936.7</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-298363.5278450283</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>2763187</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>2763187.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>20.44</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>21.09</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>21.09</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>3644523.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>4265864.6</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>4265864.6</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>4676188.2</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>5271727.56</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>5271727.56</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-205706.4754138272</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>3644523</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>3644523.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>20.66</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>21.12</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>21.12</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>2782871.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>4492107.8</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>4492107.8</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>4949433.0</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>5270788.22</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>5270788.22</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>-160421.4549616175</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>2782871</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>2782871.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>20.84</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>20.74</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>21.15</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>3118133.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>5358150.2</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>5358150.2</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>5227618.5</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>5276423.82</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>5276423.82</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>2320.626218739897</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>3118133</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>3118133.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>20.93</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>20.73</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>21.18</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>6640845.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>5738844.6</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>5738844.6</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>5385188.9</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>5245061.0</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>5245061</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>198805.5055400105</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>6640845</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>6640845.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>20.94</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>21.19</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>21.19</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>5142951.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>5009120.0</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>5009120</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>4997279.6</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>5179349.32</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>5179349.32</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>94964.56508682482</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>5142951</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>5142951.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>20.89</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>21.2</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>4775739.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>5086511.8</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>5086511.8</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>4832079.9</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>5249809.6</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>5249809.6</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>103717.4156863168</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>4775739</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>4775739.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>20.76</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>20.62</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>21.21</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>21.21</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>7113083.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>5406758.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>5406758.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>4823322.3</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>5225499.78</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>5225499.78</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>151861.4374110792</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>7113083</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>7113083.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58423,11 +57631,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>2459</t>
@@ -58609,41 +57813,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
+      <c r="AM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO134" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT134" t="inlineStr">
         <is>
           <t>0</t>
@@ -58664,20 +57864,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>0</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>0</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57890,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>0</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58059,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58243,11 @@
           <t>75.42</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>85.29</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>104.32</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>104.32</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58294,16 @@
           <t>85648038.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>52858314.6</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>52858314.6</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>66502110.5</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>152029418.66</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>152029418.66</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58320,10 @@
           <t>-10327190.58498595</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>85648038</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>85648038.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58489,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58673,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>85.68</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>105.56</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>105.56</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58724,16 @@
           <t>26842621.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>45112791.2</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>45112791.2</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>62137426.3</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>165075950.64</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>165075950.64</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58750,10 @@
           <t>-14353266.98706506</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>26842621</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>26842621.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58919,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59103,11 @@
           <t>74.55999999999999</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>86.53</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>107.09</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>86.53</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>107.09</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59154,16 @@
           <t>46276996.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>62963878.0</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>62963878</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>62826546.1</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>176676640.84</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>176676640.84</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59180,10 @@
           <t>-13291607.63335435</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>46276996</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>46276996.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59349,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59533,11 @@
           <t>76.2</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>87.57</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>108.37</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>87.56999999999999</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>108.37</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59584,16 @@
           <t>54584590.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>67074048.2</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>67074048.2</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>63270558.0</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>181106427.46</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>181106427.46</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59610,10 @@
           <t>-13382505.60543351</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>54584590</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>54584590.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59779,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59963,11 @@
           <t>79.16</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>88.62</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>109.43</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>88.62</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>109.43</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60014,16 @@
           <t>50939328.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>70495805.0</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>70495805</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>61416914.8</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>188727920.06</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>188727920.06</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60040,10 @@
           <t>-13924512.57963826</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>50939328</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>50939328.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60209,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60393,11 @@
           <t>81.47999999999999</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>89.74</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>110.41</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>89.73999999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>110.41</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60444,16 @@
           <t>46920421.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>80145906.4</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>80145906.40000001</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>63553729.6</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>200198885.5</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>200198885.5</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60470,10 @@
           <t>-13810940.45065796</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>46920421</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>46920421.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60639,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60823,11 @@
           <t>84.24</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>91.38</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>111.18</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>91.38</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>111.18</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60874,16 @@
           <t>116098055.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>79162061.4</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>79162061.40000001</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>66735382.5</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>213312167.64</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>213312167.64</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60900,10 @@
           <t>-12724849.50030547</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>116098055</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>116098055.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61069,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61253,11 @@
           <t>86.6</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>92.78</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>111.74</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>111.74</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61304,16 @@
           <t>66827847.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>62689214.2</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>62689214.2</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>66422805.7</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>218068855.1</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>218068855.1</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61330,10 @@
           <t>-18130721.44621958</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>66827847</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>66827847.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61499,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61683,11 @@
           <t>88.4</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>94.18</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>112.03</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>112.03</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61734,16 @@
           <t>71693374.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>59467067.8</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>59467067.8</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>69491458.0</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>225874374.7</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>225874374.7</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61760,10 @@
           <t>-19926919.03158905</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>71693374</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>71693374.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61929,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62113,11 @@
           <t>89.14000000000001</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>95.64</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>112.25</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>112.25</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62164,16 @@
           <t>99189835.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>52338024.6</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>52338024.6</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>71646537.6</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>236603676.32</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>236603676.32</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62190,10 @@
           <t>-22302546.36670294</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>99189835</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>99189835.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
@@ -63221,7 +62359,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -63405,15 +62543,11 @@
           <t>90.17999999999999</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>96.82</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>112.36</t>
-        </is>
+      <c r="AM145" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>112.36</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -63460,20 +62594,16 @@
           <t>42001196.0</t>
         </is>
       </c>
-      <c r="AX145" t="inlineStr">
-        <is>
-          <t>46961552.8</t>
-        </is>
+      <c r="AX145" t="n">
+        <v>46961552.8</v>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
           <t>83205574.5</t>
         </is>
       </c>
-      <c r="AZ145" t="inlineStr">
-        <is>
-          <t>243639029.84</t>
-        </is>
+      <c r="AZ145" t="n">
+        <v>243639029.84</v>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
@@ -63490,8 +62620,10 @@
           <t>-27845829.58234055</t>
         </is>
       </c>
-      <c r="BD145" t="n">
-        <v>42001196</v>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>42001196.0</t>
+        </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
